--- a/InputData/elec/RAF/Regional Availability Factor.xlsx
+++ b/InputData/elec/RAF/Regional Availability Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\Mexico\Models\eps-mexico\InputData\elec\RAF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-mexico\InputData\elec\RAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8666A19C-AA72-4666-8925-8F4E579429AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5A077A-767A-4138-B3D8-A85BF12B236A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -333,7 +333,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -874,27 +874,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{667665C7-8A8E-46D9-B686-64BA7741F669}">
   <dimension ref="A1:B35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="73.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -902,130 +902,130 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>56</v>
       </c>
@@ -1041,13 +1041,13 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:AY25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -1141,293 +1141,533 @@
       <c r="AE1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1">
+        <v>2051</v>
+      </c>
+      <c r="AG1">
+        <v>2052</v>
+      </c>
+      <c r="AH1">
+        <v>2053</v>
+      </c>
+      <c r="AI1">
+        <v>2054</v>
+      </c>
+      <c r="AJ1">
+        <v>2055</v>
+      </c>
+      <c r="AK1">
+        <v>2056</v>
+      </c>
+      <c r="AL1">
+        <v>2057</v>
+      </c>
+      <c r="AM1">
+        <v>2058</v>
+      </c>
+      <c r="AN1">
+        <v>2059</v>
+      </c>
+      <c r="AO1">
+        <v>2060</v>
+      </c>
+      <c r="AP1">
+        <v>2061</v>
+      </c>
+      <c r="AQ1">
+        <v>2062</v>
+      </c>
+      <c r="AR1">
+        <v>2063</v>
+      </c>
+      <c r="AS1">
+        <v>2064</v>
+      </c>
+      <c r="AT1">
+        <v>2065</v>
+      </c>
+      <c r="AU1">
+        <v>2066</v>
+      </c>
+      <c r="AV1">
+        <v>2067</v>
+      </c>
+      <c r="AW1">
+        <v>2068</v>
+      </c>
+      <c r="AX1">
+        <v>2069</v>
+      </c>
+      <c r="AY1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="P2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="R2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="T2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="V2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="W2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="X2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Z2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AA2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AB2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AC2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AD2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AE2">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <v>1</v>
+      </c>
+      <c r="AI2">
+        <v>1</v>
+      </c>
+      <c r="AJ2">
+        <v>1</v>
+      </c>
+      <c r="AK2">
+        <v>1</v>
+      </c>
+      <c r="AL2">
+        <v>1</v>
+      </c>
+      <c r="AM2">
+        <v>1</v>
+      </c>
+      <c r="AN2">
+        <v>1</v>
+      </c>
+      <c r="AO2">
+        <v>1</v>
+      </c>
+      <c r="AP2">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+      <c r="AR2">
+        <v>1</v>
+      </c>
+      <c r="AS2">
+        <v>1</v>
+      </c>
+      <c r="AT2">
+        <v>1</v>
+      </c>
+      <c r="AU2">
+        <v>1</v>
+      </c>
+      <c r="AV2">
+        <v>1</v>
+      </c>
+      <c r="AW2">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="P3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="T3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="V3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="W3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="X3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Z3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AA3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AB3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AC3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AD3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AE3">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF3">
+        <v>1</v>
+      </c>
+      <c r="AG3">
+        <v>1</v>
+      </c>
+      <c r="AH3">
+        <v>1</v>
+      </c>
+      <c r="AI3">
+        <v>1</v>
+      </c>
+      <c r="AJ3">
+        <v>1</v>
+      </c>
+      <c r="AK3">
+        <v>1</v>
+      </c>
+      <c r="AL3">
+        <v>1</v>
+      </c>
+      <c r="AM3">
+        <v>1</v>
+      </c>
+      <c r="AN3">
+        <v>1</v>
+      </c>
+      <c r="AO3">
+        <v>1</v>
+      </c>
+      <c r="AP3">
+        <v>1</v>
+      </c>
+      <c r="AQ3">
+        <v>1</v>
+      </c>
+      <c r="AR3">
+        <v>1</v>
+      </c>
+      <c r="AS3">
+        <v>1</v>
+      </c>
+      <c r="AT3">
+        <v>1</v>
+      </c>
+      <c r="AU3">
+        <v>1</v>
+      </c>
+      <c r="AV3">
+        <v>1</v>
+      </c>
+      <c r="AW3">
+        <v>1</v>
+      </c>
+      <c r="AX3">
+        <v>1</v>
+      </c>
+      <c r="AY3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="P4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="T4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="V4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="W4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="X4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Z4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AA4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AB4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AC4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AD4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AE4">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF4">
+        <v>1</v>
+      </c>
+      <c r="AG4">
+        <v>1</v>
+      </c>
+      <c r="AH4">
+        <v>1</v>
+      </c>
+      <c r="AI4">
+        <v>1</v>
+      </c>
+      <c r="AJ4">
+        <v>1</v>
+      </c>
+      <c r="AK4">
+        <v>1</v>
+      </c>
+      <c r="AL4">
+        <v>1</v>
+      </c>
+      <c r="AM4">
+        <v>1</v>
+      </c>
+      <c r="AN4">
+        <v>1</v>
+      </c>
+      <c r="AO4">
+        <v>1</v>
+      </c>
+      <c r="AP4">
+        <v>1</v>
+      </c>
+      <c r="AQ4">
+        <v>1</v>
+      </c>
+      <c r="AR4">
+        <v>1</v>
+      </c>
+      <c r="AS4">
+        <v>1</v>
+      </c>
+      <c r="AT4">
+        <v>1</v>
+      </c>
+      <c r="AU4">
+        <v>1</v>
+      </c>
+      <c r="AV4">
+        <v>1</v>
+      </c>
+      <c r="AW4">
+        <v>1</v>
+      </c>
+      <c r="AX4">
+        <v>1</v>
+      </c>
+      <c r="AY4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1521,8 +1761,68 @@
       <c r="AE5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:31">
+      <c r="AF5">
+        <v>1</v>
+      </c>
+      <c r="AG5">
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <v>1</v>
+      </c>
+      <c r="AM5">
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <v>1</v>
+      </c>
+      <c r="AO5">
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <v>1</v>
+      </c>
+      <c r="AQ5">
+        <v>1</v>
+      </c>
+      <c r="AR5">
+        <v>1</v>
+      </c>
+      <c r="AS5">
+        <v>1</v>
+      </c>
+      <c r="AT5">
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <v>1</v>
+      </c>
+      <c r="AV5">
+        <v>1</v>
+      </c>
+      <c r="AW5">
+        <v>1</v>
+      </c>
+      <c r="AX5">
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1616,8 +1916,68 @@
       <c r="AE6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:31">
+      <c r="AF6">
+        <v>1</v>
+      </c>
+      <c r="AG6">
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <v>1</v>
+      </c>
+      <c r="AJ6">
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <v>1</v>
+      </c>
+      <c r="AM6">
+        <v>1</v>
+      </c>
+      <c r="AN6">
+        <v>1</v>
+      </c>
+      <c r="AO6">
+        <v>1</v>
+      </c>
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
+      <c r="AR6">
+        <v>1</v>
+      </c>
+      <c r="AS6">
+        <v>1</v>
+      </c>
+      <c r="AT6">
+        <v>1</v>
+      </c>
+      <c r="AU6">
+        <v>1</v>
+      </c>
+      <c r="AV6">
+        <v>1</v>
+      </c>
+      <c r="AW6">
+        <v>1</v>
+      </c>
+      <c r="AX6">
+        <v>1</v>
+      </c>
+      <c r="AY6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1711,8 +2071,68 @@
       <c r="AE7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:31">
+      <c r="AF7">
+        <v>1</v>
+      </c>
+      <c r="AG7">
+        <v>1</v>
+      </c>
+      <c r="AH7">
+        <v>1</v>
+      </c>
+      <c r="AI7">
+        <v>1</v>
+      </c>
+      <c r="AJ7">
+        <v>1</v>
+      </c>
+      <c r="AK7">
+        <v>1</v>
+      </c>
+      <c r="AL7">
+        <v>1</v>
+      </c>
+      <c r="AM7">
+        <v>1</v>
+      </c>
+      <c r="AN7">
+        <v>1</v>
+      </c>
+      <c r="AO7">
+        <v>1</v>
+      </c>
+      <c r="AP7">
+        <v>1</v>
+      </c>
+      <c r="AQ7">
+        <v>1</v>
+      </c>
+      <c r="AR7">
+        <v>1</v>
+      </c>
+      <c r="AS7">
+        <v>1</v>
+      </c>
+      <c r="AT7">
+        <v>1</v>
+      </c>
+      <c r="AU7">
+        <v>1</v>
+      </c>
+      <c r="AV7">
+        <v>1</v>
+      </c>
+      <c r="AW7">
+        <v>1</v>
+      </c>
+      <c r="AX7">
+        <v>1</v>
+      </c>
+      <c r="AY7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1806,8 +2226,68 @@
       <c r="AE8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:31">
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <v>1</v>
+      </c>
+      <c r="AJ8">
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>1</v>
+      </c>
+      <c r="AM8">
+        <v>1</v>
+      </c>
+      <c r="AN8">
+        <v>1</v>
+      </c>
+      <c r="AO8">
+        <v>1</v>
+      </c>
+      <c r="AP8">
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <v>1</v>
+      </c>
+      <c r="AS8">
+        <v>1</v>
+      </c>
+      <c r="AT8">
+        <v>1</v>
+      </c>
+      <c r="AU8">
+        <v>1</v>
+      </c>
+      <c r="AV8">
+        <v>1</v>
+      </c>
+      <c r="AW8">
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <v>1</v>
+      </c>
+      <c r="AY8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1901,8 +2381,68 @@
       <c r="AE9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:31">
+      <c r="AF9">
+        <v>1</v>
+      </c>
+      <c r="AG9">
+        <v>1</v>
+      </c>
+      <c r="AH9">
+        <v>1</v>
+      </c>
+      <c r="AI9">
+        <v>1</v>
+      </c>
+      <c r="AJ9">
+        <v>1</v>
+      </c>
+      <c r="AK9">
+        <v>1</v>
+      </c>
+      <c r="AL9">
+        <v>1</v>
+      </c>
+      <c r="AM9">
+        <v>1</v>
+      </c>
+      <c r="AN9">
+        <v>1</v>
+      </c>
+      <c r="AO9">
+        <v>1</v>
+      </c>
+      <c r="AP9">
+        <v>1</v>
+      </c>
+      <c r="AQ9">
+        <v>1</v>
+      </c>
+      <c r="AR9">
+        <v>1</v>
+      </c>
+      <c r="AS9">
+        <v>1</v>
+      </c>
+      <c r="AT9">
+        <v>1</v>
+      </c>
+      <c r="AU9">
+        <v>1</v>
+      </c>
+      <c r="AV9">
+        <v>1</v>
+      </c>
+      <c r="AW9">
+        <v>1</v>
+      </c>
+      <c r="AX9">
+        <v>1</v>
+      </c>
+      <c r="AY9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1996,8 +2536,68 @@
       <c r="AE10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:31">
+      <c r="AF10">
+        <v>1</v>
+      </c>
+      <c r="AG10">
+        <v>1</v>
+      </c>
+      <c r="AH10">
+        <v>1</v>
+      </c>
+      <c r="AI10">
+        <v>1</v>
+      </c>
+      <c r="AJ10">
+        <v>1</v>
+      </c>
+      <c r="AK10">
+        <v>1</v>
+      </c>
+      <c r="AL10">
+        <v>1</v>
+      </c>
+      <c r="AM10">
+        <v>1</v>
+      </c>
+      <c r="AN10">
+        <v>1</v>
+      </c>
+      <c r="AO10">
+        <v>1</v>
+      </c>
+      <c r="AP10">
+        <v>1</v>
+      </c>
+      <c r="AQ10">
+        <v>1</v>
+      </c>
+      <c r="AR10">
+        <v>1</v>
+      </c>
+      <c r="AS10">
+        <v>1</v>
+      </c>
+      <c r="AT10">
+        <v>1</v>
+      </c>
+      <c r="AU10">
+        <v>1</v>
+      </c>
+      <c r="AV10">
+        <v>1</v>
+      </c>
+      <c r="AW10">
+        <v>1</v>
+      </c>
+      <c r="AX10">
+        <v>1</v>
+      </c>
+      <c r="AY10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2091,8 +2691,68 @@
       <c r="AE11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:31">
+      <c r="AF11">
+        <v>1</v>
+      </c>
+      <c r="AG11">
+        <v>1</v>
+      </c>
+      <c r="AH11">
+        <v>1</v>
+      </c>
+      <c r="AI11">
+        <v>1</v>
+      </c>
+      <c r="AJ11">
+        <v>1</v>
+      </c>
+      <c r="AK11">
+        <v>1</v>
+      </c>
+      <c r="AL11">
+        <v>1</v>
+      </c>
+      <c r="AM11">
+        <v>1</v>
+      </c>
+      <c r="AN11">
+        <v>1</v>
+      </c>
+      <c r="AO11">
+        <v>1</v>
+      </c>
+      <c r="AP11">
+        <v>1</v>
+      </c>
+      <c r="AQ11">
+        <v>1</v>
+      </c>
+      <c r="AR11">
+        <v>1</v>
+      </c>
+      <c r="AS11">
+        <v>1</v>
+      </c>
+      <c r="AT11">
+        <v>1</v>
+      </c>
+      <c r="AU11">
+        <v>1</v>
+      </c>
+      <c r="AV11">
+        <v>1</v>
+      </c>
+      <c r="AW11">
+        <v>1</v>
+      </c>
+      <c r="AX11">
+        <v>1</v>
+      </c>
+      <c r="AY11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2186,103 +2846,223 @@
       <c r="AE12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:31">
+      <c r="AF12">
+        <v>1</v>
+      </c>
+      <c r="AG12">
+        <v>1</v>
+      </c>
+      <c r="AH12">
+        <v>1</v>
+      </c>
+      <c r="AI12">
+        <v>1</v>
+      </c>
+      <c r="AJ12">
+        <v>1</v>
+      </c>
+      <c r="AK12">
+        <v>1</v>
+      </c>
+      <c r="AL12">
+        <v>1</v>
+      </c>
+      <c r="AM12">
+        <v>1</v>
+      </c>
+      <c r="AN12">
+        <v>1</v>
+      </c>
+      <c r="AO12">
+        <v>1</v>
+      </c>
+      <c r="AP12">
+        <v>1</v>
+      </c>
+      <c r="AQ12">
+        <v>1</v>
+      </c>
+      <c r="AR12">
+        <v>1</v>
+      </c>
+      <c r="AS12">
+        <v>1</v>
+      </c>
+      <c r="AT12">
+        <v>1</v>
+      </c>
+      <c r="AU12">
+        <v>1</v>
+      </c>
+      <c r="AV12">
+        <v>1</v>
+      </c>
+      <c r="AW12">
+        <v>1</v>
+      </c>
+      <c r="AX12">
+        <v>1</v>
+      </c>
+      <c r="AY12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="P13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="R13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="T13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="U13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="V13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="W13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="X13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Z13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AA13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AB13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AC13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AD13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AE13">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF13">
+        <v>1</v>
+      </c>
+      <c r="AG13">
+        <v>1</v>
+      </c>
+      <c r="AH13">
+        <v>1</v>
+      </c>
+      <c r="AI13">
+        <v>1</v>
+      </c>
+      <c r="AJ13">
+        <v>1</v>
+      </c>
+      <c r="AK13">
+        <v>1</v>
+      </c>
+      <c r="AL13">
+        <v>1</v>
+      </c>
+      <c r="AM13">
+        <v>1</v>
+      </c>
+      <c r="AN13">
+        <v>1</v>
+      </c>
+      <c r="AO13">
+        <v>1</v>
+      </c>
+      <c r="AP13">
+        <v>1</v>
+      </c>
+      <c r="AQ13">
+        <v>1</v>
+      </c>
+      <c r="AR13">
+        <v>1</v>
+      </c>
+      <c r="AS13">
+        <v>1</v>
+      </c>
+      <c r="AT13">
+        <v>1</v>
+      </c>
+      <c r="AU13">
+        <v>1</v>
+      </c>
+      <c r="AV13">
+        <v>1</v>
+      </c>
+      <c r="AW13">
+        <v>1</v>
+      </c>
+      <c r="AX13">
+        <v>1</v>
+      </c>
+      <c r="AY13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2376,8 +3156,68 @@
       <c r="AE14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:31">
+      <c r="AF14">
+        <v>1</v>
+      </c>
+      <c r="AG14">
+        <v>1</v>
+      </c>
+      <c r="AH14">
+        <v>1</v>
+      </c>
+      <c r="AI14">
+        <v>1</v>
+      </c>
+      <c r="AJ14">
+        <v>1</v>
+      </c>
+      <c r="AK14">
+        <v>1</v>
+      </c>
+      <c r="AL14">
+        <v>1</v>
+      </c>
+      <c r="AM14">
+        <v>1</v>
+      </c>
+      <c r="AN14">
+        <v>1</v>
+      </c>
+      <c r="AO14">
+        <v>1</v>
+      </c>
+      <c r="AP14">
+        <v>1</v>
+      </c>
+      <c r="AQ14">
+        <v>1</v>
+      </c>
+      <c r="AR14">
+        <v>1</v>
+      </c>
+      <c r="AS14">
+        <v>1</v>
+      </c>
+      <c r="AT14">
+        <v>1</v>
+      </c>
+      <c r="AU14">
+        <v>1</v>
+      </c>
+      <c r="AV14">
+        <v>1</v>
+      </c>
+      <c r="AW14">
+        <v>1</v>
+      </c>
+      <c r="AX14">
+        <v>1</v>
+      </c>
+      <c r="AY14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2471,8 +3311,68 @@
       <c r="AE15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:31">
+      <c r="AF15">
+        <v>1</v>
+      </c>
+      <c r="AG15">
+        <v>1</v>
+      </c>
+      <c r="AH15">
+        <v>1</v>
+      </c>
+      <c r="AI15">
+        <v>1</v>
+      </c>
+      <c r="AJ15">
+        <v>1</v>
+      </c>
+      <c r="AK15">
+        <v>1</v>
+      </c>
+      <c r="AL15">
+        <v>1</v>
+      </c>
+      <c r="AM15">
+        <v>1</v>
+      </c>
+      <c r="AN15">
+        <v>1</v>
+      </c>
+      <c r="AO15">
+        <v>1</v>
+      </c>
+      <c r="AP15">
+        <v>1</v>
+      </c>
+      <c r="AQ15">
+        <v>1</v>
+      </c>
+      <c r="AR15">
+        <v>1</v>
+      </c>
+      <c r="AS15">
+        <v>1</v>
+      </c>
+      <c r="AT15">
+        <v>1</v>
+      </c>
+      <c r="AU15">
+        <v>1</v>
+      </c>
+      <c r="AV15">
+        <v>1</v>
+      </c>
+      <c r="AW15">
+        <v>1</v>
+      </c>
+      <c r="AX15">
+        <v>1</v>
+      </c>
+      <c r="AY15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2566,8 +3466,68 @@
       <c r="AE16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:31">
+      <c r="AF16">
+        <v>1</v>
+      </c>
+      <c r="AG16">
+        <v>1</v>
+      </c>
+      <c r="AH16">
+        <v>1</v>
+      </c>
+      <c r="AI16">
+        <v>1</v>
+      </c>
+      <c r="AJ16">
+        <v>1</v>
+      </c>
+      <c r="AK16">
+        <v>1</v>
+      </c>
+      <c r="AL16">
+        <v>1</v>
+      </c>
+      <c r="AM16">
+        <v>1</v>
+      </c>
+      <c r="AN16">
+        <v>1</v>
+      </c>
+      <c r="AO16">
+        <v>1</v>
+      </c>
+      <c r="AP16">
+        <v>1</v>
+      </c>
+      <c r="AQ16">
+        <v>1</v>
+      </c>
+      <c r="AR16">
+        <v>1</v>
+      </c>
+      <c r="AS16">
+        <v>1</v>
+      </c>
+      <c r="AT16">
+        <v>1</v>
+      </c>
+      <c r="AU16">
+        <v>1</v>
+      </c>
+      <c r="AV16">
+        <v>1</v>
+      </c>
+      <c r="AW16">
+        <v>1</v>
+      </c>
+      <c r="AX16">
+        <v>1</v>
+      </c>
+      <c r="AY16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2661,8 +3621,68 @@
       <c r="AE17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:31">
+      <c r="AF17">
+        <v>1</v>
+      </c>
+      <c r="AG17">
+        <v>1</v>
+      </c>
+      <c r="AH17">
+        <v>1</v>
+      </c>
+      <c r="AI17">
+        <v>1</v>
+      </c>
+      <c r="AJ17">
+        <v>1</v>
+      </c>
+      <c r="AK17">
+        <v>1</v>
+      </c>
+      <c r="AL17">
+        <v>1</v>
+      </c>
+      <c r="AM17">
+        <v>1</v>
+      </c>
+      <c r="AN17">
+        <v>1</v>
+      </c>
+      <c r="AO17">
+        <v>1</v>
+      </c>
+      <c r="AP17">
+        <v>1</v>
+      </c>
+      <c r="AQ17">
+        <v>1</v>
+      </c>
+      <c r="AR17">
+        <v>1</v>
+      </c>
+      <c r="AS17">
+        <v>1</v>
+      </c>
+      <c r="AT17">
+        <v>1</v>
+      </c>
+      <c r="AU17">
+        <v>1</v>
+      </c>
+      <c r="AV17">
+        <v>1</v>
+      </c>
+      <c r="AW17">
+        <v>1</v>
+      </c>
+      <c r="AX17">
+        <v>1</v>
+      </c>
+      <c r="AY17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2756,8 +3776,68 @@
       <c r="AE18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:31">
+      <c r="AF18">
+        <v>1</v>
+      </c>
+      <c r="AG18">
+        <v>1</v>
+      </c>
+      <c r="AH18">
+        <v>1</v>
+      </c>
+      <c r="AI18">
+        <v>1</v>
+      </c>
+      <c r="AJ18">
+        <v>1</v>
+      </c>
+      <c r="AK18">
+        <v>1</v>
+      </c>
+      <c r="AL18">
+        <v>1</v>
+      </c>
+      <c r="AM18">
+        <v>1</v>
+      </c>
+      <c r="AN18">
+        <v>1</v>
+      </c>
+      <c r="AO18">
+        <v>1</v>
+      </c>
+      <c r="AP18">
+        <v>1</v>
+      </c>
+      <c r="AQ18">
+        <v>1</v>
+      </c>
+      <c r="AR18">
+        <v>1</v>
+      </c>
+      <c r="AS18">
+        <v>1</v>
+      </c>
+      <c r="AT18">
+        <v>1</v>
+      </c>
+      <c r="AU18">
+        <v>1</v>
+      </c>
+      <c r="AV18">
+        <v>1</v>
+      </c>
+      <c r="AW18">
+        <v>1</v>
+      </c>
+      <c r="AX18">
+        <v>1</v>
+      </c>
+      <c r="AY18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2851,8 +3931,68 @@
       <c r="AE19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:31">
+      <c r="AF19">
+        <v>1</v>
+      </c>
+      <c r="AG19">
+        <v>1</v>
+      </c>
+      <c r="AH19">
+        <v>1</v>
+      </c>
+      <c r="AI19">
+        <v>1</v>
+      </c>
+      <c r="AJ19">
+        <v>1</v>
+      </c>
+      <c r="AK19">
+        <v>1</v>
+      </c>
+      <c r="AL19">
+        <v>1</v>
+      </c>
+      <c r="AM19">
+        <v>1</v>
+      </c>
+      <c r="AN19">
+        <v>1</v>
+      </c>
+      <c r="AO19">
+        <v>1</v>
+      </c>
+      <c r="AP19">
+        <v>1</v>
+      </c>
+      <c r="AQ19">
+        <v>1</v>
+      </c>
+      <c r="AR19">
+        <v>1</v>
+      </c>
+      <c r="AS19">
+        <v>1</v>
+      </c>
+      <c r="AT19">
+        <v>1</v>
+      </c>
+      <c r="AU19">
+        <v>1</v>
+      </c>
+      <c r="AV19">
+        <v>1</v>
+      </c>
+      <c r="AW19">
+        <v>1</v>
+      </c>
+      <c r="AX19">
+        <v>1</v>
+      </c>
+      <c r="AY19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2946,8 +4086,68 @@
       <c r="AE20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:31">
+      <c r="AF20">
+        <v>1</v>
+      </c>
+      <c r="AG20">
+        <v>1</v>
+      </c>
+      <c r="AH20">
+        <v>1</v>
+      </c>
+      <c r="AI20">
+        <v>1</v>
+      </c>
+      <c r="AJ20">
+        <v>1</v>
+      </c>
+      <c r="AK20">
+        <v>1</v>
+      </c>
+      <c r="AL20">
+        <v>1</v>
+      </c>
+      <c r="AM20">
+        <v>1</v>
+      </c>
+      <c r="AN20">
+        <v>1</v>
+      </c>
+      <c r="AO20">
+        <v>1</v>
+      </c>
+      <c r="AP20">
+        <v>1</v>
+      </c>
+      <c r="AQ20">
+        <v>1</v>
+      </c>
+      <c r="AR20">
+        <v>1</v>
+      </c>
+      <c r="AS20">
+        <v>1</v>
+      </c>
+      <c r="AT20">
+        <v>1</v>
+      </c>
+      <c r="AU20">
+        <v>1</v>
+      </c>
+      <c r="AV20">
+        <v>1</v>
+      </c>
+      <c r="AW20">
+        <v>1</v>
+      </c>
+      <c r="AX20">
+        <v>1</v>
+      </c>
+      <c r="AY20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3041,8 +4241,68 @@
       <c r="AE21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:31">
+      <c r="AF21">
+        <v>1</v>
+      </c>
+      <c r="AG21">
+        <v>1</v>
+      </c>
+      <c r="AH21">
+        <v>1</v>
+      </c>
+      <c r="AI21">
+        <v>1</v>
+      </c>
+      <c r="AJ21">
+        <v>1</v>
+      </c>
+      <c r="AK21">
+        <v>1</v>
+      </c>
+      <c r="AL21">
+        <v>1</v>
+      </c>
+      <c r="AM21">
+        <v>1</v>
+      </c>
+      <c r="AN21">
+        <v>1</v>
+      </c>
+      <c r="AO21">
+        <v>1</v>
+      </c>
+      <c r="AP21">
+        <v>1</v>
+      </c>
+      <c r="AQ21">
+        <v>1</v>
+      </c>
+      <c r="AR21">
+        <v>1</v>
+      </c>
+      <c r="AS21">
+        <v>1</v>
+      </c>
+      <c r="AT21">
+        <v>1</v>
+      </c>
+      <c r="AU21">
+        <v>1</v>
+      </c>
+      <c r="AV21">
+        <v>1</v>
+      </c>
+      <c r="AW21">
+        <v>1</v>
+      </c>
+      <c r="AX21">
+        <v>1</v>
+      </c>
+      <c r="AY21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -3136,8 +4396,68 @@
       <c r="AE22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:31">
+      <c r="AF22">
+        <v>1</v>
+      </c>
+      <c r="AG22">
+        <v>1</v>
+      </c>
+      <c r="AH22">
+        <v>1</v>
+      </c>
+      <c r="AI22">
+        <v>1</v>
+      </c>
+      <c r="AJ22">
+        <v>1</v>
+      </c>
+      <c r="AK22">
+        <v>1</v>
+      </c>
+      <c r="AL22">
+        <v>1</v>
+      </c>
+      <c r="AM22">
+        <v>1</v>
+      </c>
+      <c r="AN22">
+        <v>1</v>
+      </c>
+      <c r="AO22">
+        <v>1</v>
+      </c>
+      <c r="AP22">
+        <v>1</v>
+      </c>
+      <c r="AQ22">
+        <v>1</v>
+      </c>
+      <c r="AR22">
+        <v>1</v>
+      </c>
+      <c r="AS22">
+        <v>1</v>
+      </c>
+      <c r="AT22">
+        <v>1</v>
+      </c>
+      <c r="AU22">
+        <v>1</v>
+      </c>
+      <c r="AV22">
+        <v>1</v>
+      </c>
+      <c r="AW22">
+        <v>1</v>
+      </c>
+      <c r="AX22">
+        <v>1</v>
+      </c>
+      <c r="AY22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -3231,8 +4551,68 @@
       <c r="AE23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:31">
+      <c r="AF23">
+        <v>1</v>
+      </c>
+      <c r="AG23">
+        <v>1</v>
+      </c>
+      <c r="AH23">
+        <v>1</v>
+      </c>
+      <c r="AI23">
+        <v>1</v>
+      </c>
+      <c r="AJ23">
+        <v>1</v>
+      </c>
+      <c r="AK23">
+        <v>1</v>
+      </c>
+      <c r="AL23">
+        <v>1</v>
+      </c>
+      <c r="AM23">
+        <v>1</v>
+      </c>
+      <c r="AN23">
+        <v>1</v>
+      </c>
+      <c r="AO23">
+        <v>1</v>
+      </c>
+      <c r="AP23">
+        <v>1</v>
+      </c>
+      <c r="AQ23">
+        <v>1</v>
+      </c>
+      <c r="AR23">
+        <v>1</v>
+      </c>
+      <c r="AS23">
+        <v>1</v>
+      </c>
+      <c r="AT23">
+        <v>1</v>
+      </c>
+      <c r="AU23">
+        <v>1</v>
+      </c>
+      <c r="AV23">
+        <v>1</v>
+      </c>
+      <c r="AW23">
+        <v>1</v>
+      </c>
+      <c r="AX23">
+        <v>1</v>
+      </c>
+      <c r="AY23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -3326,8 +4706,68 @@
       <c r="AE24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:31">
+      <c r="AF24">
+        <v>1</v>
+      </c>
+      <c r="AG24">
+        <v>1</v>
+      </c>
+      <c r="AH24">
+        <v>1</v>
+      </c>
+      <c r="AI24">
+        <v>1</v>
+      </c>
+      <c r="AJ24">
+        <v>1</v>
+      </c>
+      <c r="AK24">
+        <v>1</v>
+      </c>
+      <c r="AL24">
+        <v>1</v>
+      </c>
+      <c r="AM24">
+        <v>1</v>
+      </c>
+      <c r="AN24">
+        <v>1</v>
+      </c>
+      <c r="AO24">
+        <v>1</v>
+      </c>
+      <c r="AP24">
+        <v>1</v>
+      </c>
+      <c r="AQ24">
+        <v>1</v>
+      </c>
+      <c r="AR24">
+        <v>1</v>
+      </c>
+      <c r="AS24">
+        <v>1</v>
+      </c>
+      <c r="AT24">
+        <v>1</v>
+      </c>
+      <c r="AU24">
+        <v>1</v>
+      </c>
+      <c r="AV24">
+        <v>1</v>
+      </c>
+      <c r="AW24">
+        <v>1</v>
+      </c>
+      <c r="AX24">
+        <v>1</v>
+      </c>
+      <c r="AY24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -3419,6 +4859,66 @@
         <v>1</v>
       </c>
       <c r="AE25">
+        <v>1</v>
+      </c>
+      <c r="AF25">
+        <v>1</v>
+      </c>
+      <c r="AG25">
+        <v>1</v>
+      </c>
+      <c r="AH25">
+        <v>1</v>
+      </c>
+      <c r="AI25">
+        <v>1</v>
+      </c>
+      <c r="AJ25">
+        <v>1</v>
+      </c>
+      <c r="AK25">
+        <v>1</v>
+      </c>
+      <c r="AL25">
+        <v>1</v>
+      </c>
+      <c r="AM25">
+        <v>1</v>
+      </c>
+      <c r="AN25">
+        <v>1</v>
+      </c>
+      <c r="AO25">
+        <v>1</v>
+      </c>
+      <c r="AP25">
+        <v>1</v>
+      </c>
+      <c r="AQ25">
+        <v>1</v>
+      </c>
+      <c r="AR25">
+        <v>1</v>
+      </c>
+      <c r="AS25">
+        <v>1</v>
+      </c>
+      <c r="AT25">
+        <v>1</v>
+      </c>
+      <c r="AU25">
+        <v>1</v>
+      </c>
+      <c r="AV25">
+        <v>1</v>
+      </c>
+      <c r="AW25">
+        <v>1</v>
+      </c>
+      <c r="AX25">
+        <v>1</v>
+      </c>
+      <c r="AY25">
         <v>1</v>
       </c>
     </row>
@@ -3433,13 +4933,13 @@
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.5703125" customWidth="1"/>
     <col min="2" max="2" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>23</v>
       </c>
@@ -3447,7 +4947,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>43</v>
       </c>
